--- a/exports/xlsx/KPI_AGE_PATHOLOGIE.xlsx
+++ b/exports/xlsx/KPI_AGE_PATHOLOGIE.xlsx
@@ -464,10 +464,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>54.857143</v>
+        <v>53.125</v>
       </c>
     </row>
     <row r="3">
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>55.666667</v>
+        <v>53.285714</v>
       </c>
     </row>
     <row r="5">
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>47.375</v>
+        <v>50.222222</v>
       </c>
     </row>
     <row r="6">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>40.714286</v>
+        <v>41.625</v>
       </c>
     </row>
     <row r="9">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>45</v>
+        <v>51.166667</v>
       </c>
     </row>
     <row r="18">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>49.8</v>
+        <v>46.166667</v>
       </c>
     </row>
     <row r="22">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>66.166667</v>
+        <v>59.428571</v>
       </c>
     </row>
     <row r="27">
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>60.125</v>
+        <v>59.111111</v>
       </c>
     </row>
     <row r="29">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="31">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>45.666667</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="52">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D57" t="n">
-        <v>64.8</v>
+        <v>62.454545</v>
       </c>
     </row>
     <row r="58">
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>43.25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D92" t="n">
-        <v>46.666667</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="93">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D111" t="n">
-        <v>61.111111</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="112">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D112" t="n">
-        <v>44</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="113">
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D119" t="n">
-        <v>60.125</v>
+        <v>61.888889</v>
       </c>
     </row>
     <row r="120">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D123" t="n">
         <v>47</v>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D133" t="n">
-        <v>53.363636</v>
+        <v>52</v>
       </c>
     </row>
     <row r="134">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D134" t="n">
-        <v>52.111111</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="135">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D140" t="n">
-        <v>51.875</v>
+        <v>53.555556</v>
       </c>
     </row>
     <row r="141">
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D144" t="n">
-        <v>51.166667</v>
+        <v>49.230769</v>
       </c>
     </row>
     <row r="145">
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D145" t="n">
-        <v>49.375</v>
+        <v>46.333333</v>
       </c>
     </row>
     <row r="146">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D152" t="n">
-        <v>52.875</v>
+        <v>52.555556</v>
       </c>
     </row>
     <row r="153">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D162" t="n">
-        <v>62.928571</v>
+        <v>64.066667</v>
       </c>
     </row>
     <row r="163">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D163" t="n">
-        <v>52</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="164">
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D190" t="n">
-        <v>59.875</v>
+        <v>63.888889</v>
       </c>
     </row>
     <row r="191">
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D204" t="n">
-        <v>61.666667</v>
+        <v>63.142857</v>
       </c>
     </row>
     <row r="205">
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D221" t="n">
-        <v>52.833333</v>
+        <v>58.285714</v>
       </c>
     </row>
     <row r="222">
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D281" t="n">
-        <v>47.545455</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="282">
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D301" t="n">
-        <v>43.6</v>
+        <v>45.166667</v>
       </c>
     </row>
     <row r="302">
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D324" t="n">
-        <v>50.666667</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="325">
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D328" t="n">
-        <v>73.166667</v>
+        <v>68.14285700000001</v>
       </c>
     </row>
     <row r="329">
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D362" t="n">
-        <v>52.3</v>
+        <v>50.636364</v>
       </c>
     </row>
     <row r="363">
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D378" t="n">
-        <v>50.5</v>
+        <v>49.222222</v>
       </c>
     </row>
     <row r="379">
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D396" t="n">
-        <v>80.5</v>
+        <v>72.333333</v>
       </c>
     </row>
     <row r="397">
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D402" t="n">
-        <v>69.421053</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="403">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D408" t="n">
-        <v>52.1875</v>
+        <v>52.588235</v>
       </c>
     </row>
     <row r="409">
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D422" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="423">
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D426" t="n">
-        <v>67.578947</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="427">
@@ -7296,10 +7296,10 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D429" t="n">
-        <v>70.2</v>
+        <v>69.363636</v>
       </c>
     </row>
     <row r="430">
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D432" t="n">
-        <v>55.3125</v>
+        <v>54.176471</v>
       </c>
     </row>
     <row r="433">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D434" t="n">
-        <v>62.214286</v>
+        <v>58.933333</v>
       </c>
     </row>
     <row r="435">
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D441" t="n">
-        <v>44.066667</v>
+        <v>46.1875</v>
       </c>
     </row>
     <row r="442">
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D443" t="n">
-        <v>51.933333</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="444">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D448" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="449">
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D462" t="n">
-        <v>61.470588</v>
+        <v>62.166667</v>
       </c>
     </row>
     <row r="463">
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D465" t="n">
-        <v>53.846154</v>
+        <v>54.285714</v>
       </c>
     </row>
     <row r="466">
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D466" t="n">
-        <v>59.785714</v>
+        <v>57.066667</v>
       </c>
     </row>
     <row r="467">
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D468" t="n">
-        <v>56.0625</v>
+        <v>57.823529</v>
       </c>
     </row>
     <row r="469">
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D469" t="n">
-        <v>50.583333</v>
+        <v>50.153846</v>
       </c>
     </row>
     <row r="470">
@@ -8192,10 +8192,10 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D485" t="n">
-        <v>50.285714</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="486">
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D486" t="n">
-        <v>56.363636</v>
+        <v>54.833333</v>
       </c>
     </row>
     <row r="487">
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D490" t="n">
-        <v>57.285714</v>
+        <v>58.517241</v>
       </c>
     </row>
     <row r="491">
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D510" t="n">
-        <v>58.833333</v>
+        <v>63.714286</v>
       </c>
     </row>
     <row r="511">
@@ -8704,10 +8704,10 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D517" t="n">
-        <v>47.333333</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="518">
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D523" t="n">
-        <v>59</v>
+        <v>61.444444</v>
       </c>
     </row>
     <row r="524">
@@ -9248,10 +9248,10 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D551" t="n">
-        <v>57.333333</v>
+        <v>59.714286</v>
       </c>
     </row>
     <row r="552">
@@ -9536,10 +9536,10 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D569" t="n">
-        <v>29.8</v>
+        <v>40.333333</v>
       </c>
     </row>
     <row r="570">
@@ -9680,10 +9680,10 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D578" t="n">
-        <v>34.25</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="579">
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D579" t="n">
-        <v>67</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="580">
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D582" t="n">
-        <v>60.4</v>
+        <v>56.666667</v>
       </c>
     </row>
     <row r="583">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D592" t="n">
-        <v>36.571429</v>
+        <v>43.875</v>
       </c>
     </row>
     <row r="593">
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="C600" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D600" t="n">
-        <v>61.25</v>
+        <v>60.222222</v>
       </c>
     </row>
     <row r="601">
@@ -10048,10 +10048,10 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D601" t="n">
-        <v>61.5</v>
+        <v>61.470588</v>
       </c>
     </row>
     <row r="602">
@@ -10192,10 +10192,10 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D610" t="n">
-        <v>67.375</v>
+        <v>70.555556</v>
       </c>
     </row>
     <row r="611">
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D622" t="n">
-        <v>44.363636</v>
+        <v>43.833333</v>
       </c>
     </row>
     <row r="623">
@@ -10480,10 +10480,10 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D628" t="n">
-        <v>61.833333</v>
+        <v>63.384615</v>
       </c>
     </row>
     <row r="629">
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="C637" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D637" t="n">
-        <v>52.52381</v>
+        <v>54.227273</v>
       </c>
     </row>
     <row r="638">
@@ -10656,10 +10656,10 @@
         </is>
       </c>
       <c r="C639" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D639" t="n">
-        <v>54.315789</v>
+        <v>53</v>
       </c>
     </row>
     <row r="640">
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="C644" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D644" t="n">
-        <v>56.875</v>
+        <v>56.941176</v>
       </c>
     </row>
     <row r="645">
@@ -10784,10 +10784,10 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D647" t="n">
-        <v>50.0625</v>
+        <v>48.647059</v>
       </c>
     </row>
     <row r="648">
@@ -10944,10 +10944,10 @@
         </is>
       </c>
       <c r="C657" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D657" t="n">
-        <v>56.846154</v>
+        <v>57.357143</v>
       </c>
     </row>
     <row r="658">
@@ -10960,10 +10960,10 @@
         </is>
       </c>
       <c r="C658" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D658" t="n">
-        <v>45.166667</v>
+        <v>47.153846</v>
       </c>
     </row>
     <row r="659">
@@ -11040,10 +11040,10 @@
         </is>
       </c>
       <c r="C663" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D663" t="n">
-        <v>47.727273</v>
+        <v>45.416667</v>
       </c>
     </row>
     <row r="664">
@@ -11088,10 +11088,10 @@
         </is>
       </c>
       <c r="C666" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D666" t="n">
-        <v>67.235294</v>
+        <v>64.38888900000001</v>
       </c>
     </row>
     <row r="667">
@@ -11264,10 +11264,10 @@
         </is>
       </c>
       <c r="C677" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D677" t="n">
-        <v>45.928571</v>
+        <v>45.133333</v>
       </c>
     </row>
     <row r="678">
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="C679" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D679" t="n">
-        <v>46.285714</v>
+        <v>46.5625</v>
       </c>
     </row>
     <row r="680">
@@ -11328,10 +11328,10 @@
         </is>
       </c>
       <c r="C681" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D681" t="n">
-        <v>59.666667</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="682">
@@ -11344,10 +11344,10 @@
         </is>
       </c>
       <c r="C682" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D682" t="n">
-        <v>50</v>
+        <v>48.333333</v>
       </c>
     </row>
     <row r="683">
@@ -11360,10 +11360,10 @@
         </is>
       </c>
       <c r="C683" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D683" t="n">
-        <v>48</v>
+        <v>45.272727</v>
       </c>
     </row>
     <row r="684">
@@ -11424,10 +11424,10 @@
         </is>
       </c>
       <c r="C687" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D687" t="n">
-        <v>51.4</v>
+        <v>53.125</v>
       </c>
     </row>
     <row r="688">
@@ -11456,10 +11456,10 @@
         </is>
       </c>
       <c r="C689" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D689" t="n">
-        <v>51.909091</v>
+        <v>48.666667</v>
       </c>
     </row>
     <row r="690">
@@ -11600,10 +11600,10 @@
         </is>
       </c>
       <c r="C698" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D698" t="n">
-        <v>54.545455</v>
+        <v>56.333333</v>
       </c>
     </row>
     <row r="699">
@@ -11632,10 +11632,10 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D700" t="n">
-        <v>53</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="701">
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D715" t="n">
-        <v>51.947368</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="716">
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D716" t="n">
-        <v>39.428571</v>
+        <v>40.875</v>
       </c>
     </row>
     <row r="717">
@@ -12160,10 +12160,10 @@
         </is>
       </c>
       <c r="C733" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D733" t="n">
-        <v>39.235294</v>
+        <v>38.388889</v>
       </c>
     </row>
     <row r="734">
@@ -12224,10 +12224,10 @@
         </is>
       </c>
       <c r="C737" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D737" t="n">
-        <v>42.294118</v>
+        <v>42.166667</v>
       </c>
     </row>
     <row r="738">
@@ -12240,10 +12240,10 @@
         </is>
       </c>
       <c r="C738" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D738" t="n">
-        <v>42.272727</v>
+        <v>46.583333</v>
       </c>
     </row>
     <row r="739">
@@ -12320,10 +12320,10 @@
         </is>
       </c>
       <c r="C743" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D743" t="n">
-        <v>51.52381</v>
+        <v>53.090909</v>
       </c>
     </row>
     <row r="744">
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D753" t="n">
-        <v>48.555556</v>
+        <v>47.473684</v>
       </c>
     </row>
     <row r="754">
@@ -12608,10 +12608,10 @@
         </is>
       </c>
       <c r="C761" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D761" t="n">
-        <v>57.533333</v>
+        <v>59</v>
       </c>
     </row>
     <row r="762">
@@ -12752,10 +12752,10 @@
         </is>
       </c>
       <c r="C770" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D770" t="n">
-        <v>62.5</v>
+        <v>62.923077</v>
       </c>
     </row>
     <row r="771">
@@ -12768,10 +12768,10 @@
         </is>
       </c>
       <c r="C771" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D771" t="n">
-        <v>51.222222</v>
+        <v>49.894737</v>
       </c>
     </row>
     <row r="772">
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="C784" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D784" t="n">
-        <v>55</v>
+        <v>54.75</v>
       </c>
     </row>
     <row r="785">
@@ -12992,10 +12992,10 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D785" t="n">
-        <v>49.454545</v>
+        <v>46.846154</v>
       </c>
     </row>
     <row r="786">
@@ -13072,10 +13072,10 @@
         </is>
       </c>
       <c r="C790" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D790" t="n">
-        <v>49.266667</v>
+        <v>46.9375</v>
       </c>
     </row>
     <row r="791">
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D803" t="n">
-        <v>42.2</v>
+        <v>44.047619</v>
       </c>
     </row>
     <row r="804">
@@ -13328,10 +13328,10 @@
         </is>
       </c>
       <c r="C806" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D806" t="n">
-        <v>42.421053</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="807">
@@ -13408,10 +13408,10 @@
         </is>
       </c>
       <c r="C811" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D811" t="n">
-        <v>54.941176</v>
+        <v>56.888889</v>
       </c>
     </row>
     <row r="812">
@@ -13456,10 +13456,10 @@
         </is>
       </c>
       <c r="C814" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D814" t="n">
-        <v>55.823529</v>
+        <v>53.444444</v>
       </c>
     </row>
     <row r="815">
@@ -13712,10 +13712,10 @@
         </is>
       </c>
       <c r="C830" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D830" t="n">
-        <v>60</v>
+        <v>62.266667</v>
       </c>
     </row>
     <row r="831">
@@ -13808,10 +13808,10 @@
         </is>
       </c>
       <c r="C836" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D836" t="n">
-        <v>36.6</v>
+        <v>36.0625</v>
       </c>
     </row>
     <row r="837">
@@ -13824,10 +13824,10 @@
         </is>
       </c>
       <c r="C837" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D837" t="n">
-        <v>47.071429</v>
+        <v>49.333333</v>
       </c>
     </row>
     <row r="838">
@@ -14048,10 +14048,10 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D851" t="n">
-        <v>46.857143</v>
+        <v>46.333333</v>
       </c>
     </row>
     <row r="852">
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="C873" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D873" t="n">
-        <v>54.526316</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="874">
@@ -14432,10 +14432,10 @@
         </is>
       </c>
       <c r="C875" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D875" t="n">
-        <v>57.071429</v>
+        <v>57.266667</v>
       </c>
     </row>
     <row r="876">
@@ -14464,10 +14464,10 @@
         </is>
       </c>
       <c r="C877" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D877" t="n">
-        <v>44.666667</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="878">
@@ -14576,10 +14576,10 @@
         </is>
       </c>
       <c r="C884" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D884" t="n">
-        <v>58.5625</v>
+        <v>59.882353</v>
       </c>
     </row>
     <row r="885">
@@ -14608,10 +14608,10 @@
         </is>
       </c>
       <c r="C886" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D886" t="n">
-        <v>53.066667</v>
+        <v>54.3125</v>
       </c>
     </row>
     <row r="887">
@@ -14720,10 +14720,10 @@
         </is>
       </c>
       <c r="C893" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D893" t="n">
-        <v>44.222222</v>
+        <v>44.157895</v>
       </c>
     </row>
     <row r="894">
@@ -14752,10 +14752,10 @@
         </is>
       </c>
       <c r="C895" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D895" t="n">
-        <v>57.695652</v>
+        <v>56.916667</v>
       </c>
     </row>
     <row r="896">
@@ -14832,10 +14832,10 @@
         </is>
       </c>
       <c r="C900" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D900" t="n">
-        <v>42.714286</v>
+        <v>44.066667</v>
       </c>
     </row>
     <row r="901">
@@ -14848,10 +14848,10 @@
         </is>
       </c>
       <c r="C901" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D901" t="n">
-        <v>47.636364</v>
+        <v>50.416667</v>
       </c>
     </row>
     <row r="902">
@@ -15056,10 +15056,10 @@
         </is>
       </c>
       <c r="C914" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D914" t="n">
-        <v>54.888889</v>
+        <v>52.684211</v>
       </c>
     </row>
     <row r="915">
@@ -15088,10 +15088,10 @@
         </is>
       </c>
       <c r="C916" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D916" t="n">
-        <v>57.833333</v>
+        <v>57.473684</v>
       </c>
     </row>
     <row r="917">
@@ -15200,10 +15200,10 @@
         </is>
       </c>
       <c r="C923" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D923" t="n">
-        <v>47.8</v>
+        <v>46.428571</v>
       </c>
     </row>
     <row r="924">
@@ -15376,10 +15376,10 @@
         </is>
       </c>
       <c r="C934" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D934" t="n">
-        <v>41.428571</v>
+        <v>44.133333</v>
       </c>
     </row>
     <row r="935">
@@ -15504,10 +15504,10 @@
         </is>
       </c>
       <c r="C942" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D942" t="n">
-        <v>46.933333</v>
+        <v>48.625</v>
       </c>
     </row>
     <row r="943">
@@ -15584,10 +15584,10 @@
         </is>
       </c>
       <c r="C947" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D947" t="n">
-        <v>58.416667</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="948">
@@ -15600,10 +15600,10 @@
         </is>
       </c>
       <c r="C948" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D948" t="n">
-        <v>41.8</v>
+        <v>42.8125</v>
       </c>
     </row>
     <row r="949">
@@ -15712,10 +15712,10 @@
         </is>
       </c>
       <c r="C955" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D955" t="n">
-        <v>45.6875</v>
+        <v>44.411765</v>
       </c>
     </row>
     <row r="956">
@@ -15808,10 +15808,10 @@
         </is>
       </c>
       <c r="C961" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D961" t="n">
-        <v>48.346154</v>
+        <v>49.37037</v>
       </c>
     </row>
     <row r="962">
@@ -15872,10 +15872,10 @@
         </is>
       </c>
       <c r="C965" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D965" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="966">
@@ -15936,10 +15936,10 @@
         </is>
       </c>
       <c r="C969" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D969" t="n">
-        <v>51.285714</v>
+        <v>49.933333</v>
       </c>
     </row>
     <row r="970">
@@ -15952,10 +15952,10 @@
         </is>
       </c>
       <c r="C970" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D970" t="n">
-        <v>49.055556</v>
+        <v>48.052632</v>
       </c>
     </row>
     <row r="971">
@@ -15968,10 +15968,10 @@
         </is>
       </c>
       <c r="C971" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D971" t="n">
-        <v>52.666667</v>
+        <v>51.764706</v>
       </c>
     </row>
     <row r="972">
@@ -16000,10 +16000,10 @@
         </is>
       </c>
       <c r="C973" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D973" t="n">
-        <v>46.333333</v>
+        <v>44.8125</v>
       </c>
     </row>
     <row r="974">
@@ -16016,10 +16016,10 @@
         </is>
       </c>
       <c r="C974" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D974" t="n">
-        <v>56.578947</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="975">
@@ -16224,10 +16224,10 @@
         </is>
       </c>
       <c r="C987" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D987" t="n">
-        <v>68.2</v>
+        <v>66.9375</v>
       </c>
     </row>
     <row r="988">
@@ -16240,10 +16240,10 @@
         </is>
       </c>
       <c r="C988" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D988" t="n">
-        <v>47.823529</v>
+        <v>49.111111</v>
       </c>
     </row>
     <row r="989">
@@ -16480,10 +16480,10 @@
         </is>
       </c>
       <c r="C1003" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D1003" t="n">
-        <v>46.9</v>
+        <v>45.090909</v>
       </c>
     </row>
     <row r="1004">
@@ -16784,10 +16784,10 @@
         </is>
       </c>
       <c r="C1022" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1022" t="n">
-        <v>54</v>
+        <v>52.625</v>
       </c>
     </row>
     <row r="1023">
@@ -16800,10 +16800,10 @@
         </is>
       </c>
       <c r="C1023" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1023" t="n">
-        <v>37.666667</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="1024">
@@ -16848,10 +16848,10 @@
         </is>
       </c>
       <c r="C1026" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1026" t="n">
-        <v>44.666667</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="1027">
@@ -17408,10 +17408,10 @@
         </is>
       </c>
       <c r="C1061" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1061" t="n">
-        <v>50.666667</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="1062">
@@ -17616,10 +17616,10 @@
         </is>
       </c>
       <c r="C1074" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1074" t="n">
-        <v>45.285714</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1075">
@@ -17936,10 +17936,10 @@
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1094" t="n">
-        <v>48.357143</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1095">
@@ -18080,10 +18080,10 @@
         </is>
       </c>
       <c r="C1103" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1103" t="n">
-        <v>52.529412</v>
+        <v>53.166667</v>
       </c>
     </row>
     <row r="1104">
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="C1104" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1104" t="n">
-        <v>39.578947</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="1105">
@@ -18160,10 +18160,10 @@
         </is>
       </c>
       <c r="C1108" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1108" t="n">
-        <v>53.26087</v>
+        <v>53.791667</v>
       </c>
     </row>
     <row r="1109">
@@ -18272,10 +18272,10 @@
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1115" t="n">
-        <v>52.117647</v>
+        <v>52.333333</v>
       </c>
     </row>
     <row r="1116">
@@ -18320,10 +18320,10 @@
         </is>
       </c>
       <c r="C1118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1118" t="n">
-        <v>54.055556</v>
+        <v>54.105263</v>
       </c>
     </row>
     <row r="1119">
@@ -18352,10 +18352,10 @@
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1120" t="n">
-        <v>52.238095</v>
+        <v>52.227273</v>
       </c>
     </row>
     <row r="1121">
@@ -18448,10 +18448,10 @@
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1126" t="n">
-        <v>60.111111</v>
+        <v>61.947368</v>
       </c>
     </row>
     <row r="1127">
@@ -18464,10 +18464,10 @@
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1127" t="n">
-        <v>46.857143</v>
+        <v>46.090909</v>
       </c>
     </row>
     <row r="1128">
@@ -18528,10 +18528,10 @@
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1131" t="n">
-        <v>39.642857</v>
+        <v>42.466667</v>
       </c>
     </row>
     <row r="1132">
@@ -18592,10 +18592,10 @@
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1135" t="n">
-        <v>52.944444</v>
+        <v>52.473684</v>
       </c>
     </row>
     <row r="1136">
@@ -18608,10 +18608,10 @@
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D1136" t="n">
-        <v>48.571429</v>
+        <v>46.130435</v>
       </c>
     </row>
     <row r="1137">
@@ -18768,10 +18768,10 @@
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1146" t="n">
-        <v>44</v>
+        <v>45.785714</v>
       </c>
     </row>
     <row r="1147">
@@ -18864,10 +18864,10 @@
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1152" t="n">
-        <v>33.538462</v>
+        <v>35.428571</v>
       </c>
     </row>
     <row r="1153">
@@ -18880,10 +18880,10 @@
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1153" t="n">
-        <v>54.2</v>
+        <v>55.875</v>
       </c>
     </row>
     <row r="1154">
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1155" t="n">
-        <v>48.904762</v>
+        <v>47.409091</v>
       </c>
     </row>
     <row r="1156">
@@ -18928,10 +18928,10 @@
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1156" t="n">
-        <v>60.26087</v>
+        <v>59.541667</v>
       </c>
     </row>
     <row r="1157">
@@ -19072,10 +19072,10 @@
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1165" t="n">
-        <v>45.764706</v>
+        <v>45.388889</v>
       </c>
     </row>
     <row r="1166">
@@ -19264,10 +19264,10 @@
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1177" t="n">
-        <v>48.111111</v>
+        <v>47.684211</v>
       </c>
     </row>
     <row r="1178">
@@ -19296,10 +19296,10 @@
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1179" t="n">
-        <v>57.75</v>
+        <v>59.117647</v>
       </c>
     </row>
     <row r="1180">
@@ -19328,10 +19328,10 @@
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1181" t="n">
-        <v>56.058824</v>
+        <v>58.166667</v>
       </c>
     </row>
     <row r="1182">
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1183" t="n">
-        <v>51.357143</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="1184">
@@ -19408,10 +19408,10 @@
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1186" t="n">
-        <v>53.684211</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="1187">
@@ -19424,10 +19424,10 @@
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1187" t="n">
-        <v>53</v>
+        <v>53.208333</v>
       </c>
     </row>
     <row r="1188">
